--- a/StructureDefinition-tk-api-specification-source-reference.xlsx
+++ b/StructureDefinition-tk-api-specification-source-reference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T06:56:47+00:00</t>
+    <t>2026-09-10T07:38:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
